--- a/esyluban/examples/dev/DataTables/test/test_null_datas/test_null.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_null_datas/test_null.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="13.125" customWidth="1" style="4" min="5" max="5"/>
@@ -459,7 +459,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestNull" &amp; value_type="test.TestNull" &amp; read_schema_from_file="false" &amp; input="test/test_null_datas" &amp; output="test_tbtestnull"</t>
+          <t>full_name="test.TbTestNull" &amp; input="test/test_null_datas"</t>
         </is>
       </c>
     </row>
@@ -512,8 +512,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="0" t="n">
         <v>1</v>
@@ -670,16 +668,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E1:F1"/>

--- a/esyluban/examples/dev/DataTables/test/test_null_datas/test_null.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_null_datas/test_null.xlsx
@@ -670,8 +670,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
